--- a/artfynd/A 8315-2026 artfynd.xlsx
+++ b/artfynd/A 8315-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,442 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132836699</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Misseröd ädellöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>412564</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6200898</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132836957</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Misseröd ädellöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>412564</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6200898</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132836326</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bokehall, Misseröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>412469</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6200774</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132836639</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57247</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Misseröd ädellöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>412564</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6200898</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8315-2026 artfynd.xlsx
+++ b/artfynd/A 8315-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>132836699</v>
       </c>
       <c r="B3" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>132836957</v>
       </c>
       <c r="B4" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>132836326</v>
       </c>
       <c r="B5" t="n">
-        <v>58238</v>
+        <v>58239</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>132836639</v>
       </c>
       <c r="B6" t="n">
-        <v>57247</v>
+        <v>57248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8315-2026 artfynd.xlsx
+++ b/artfynd/A 8315-2026 artfynd.xlsx
@@ -777,27 +777,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132836699</v>
+        <v>132836957</v>
       </c>
       <c r="B3" t="n">
-        <v>58328</v>
+        <v>57951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -886,27 +886,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132836957</v>
+        <v>132836699</v>
       </c>
       <c r="B4" t="n">
-        <v>57951</v>
+        <v>58328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 8315-2026 artfynd.xlsx
+++ b/artfynd/A 8315-2026 artfynd.xlsx
@@ -777,27 +777,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132836957</v>
+        <v>132836699</v>
       </c>
       <c r="B3" t="n">
-        <v>57951</v>
+        <v>58328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -886,27 +886,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132836699</v>
+        <v>132836957</v>
       </c>
       <c r="B4" t="n">
-        <v>58328</v>
+        <v>57951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 8315-2026 artfynd.xlsx
+++ b/artfynd/A 8315-2026 artfynd.xlsx
@@ -777,27 +777,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132836957</v>
+        <v>132836699</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>58332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -886,27 +886,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132836699</v>
+        <v>132836957</v>
       </c>
       <c r="B4" t="n">
-        <v>58332</v>
+        <v>57955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 8315-2026 artfynd.xlsx
+++ b/artfynd/A 8315-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129362463</v>
       </c>
       <c r="B2" t="n">
-        <v>102269</v>
+        <v>102646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132836699</v>
+        <v>132836639</v>
       </c>
       <c r="B3" t="n">
-        <v>58332</v>
+        <v>57269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,26 +788,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -889,11 +889,11 @@
         <v>132836957</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -998,7 +998,7 @@
         <v>132836326</v>
       </c>
       <c r="B5" t="n">
-        <v>58243</v>
+        <v>58260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132836639</v>
+        <v>132836699</v>
       </c>
       <c r="B6" t="n">
-        <v>57252</v>
+        <v>58349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,26 +1115,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100038</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>

--- a/artfynd/A 8315-2026 artfynd.xlsx
+++ b/artfynd/A 8315-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129362463</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132836639</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132836957</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132836326</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,8 +1235,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132836699</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>